--- a/r4-JoanneumResearch-PreNUDGE-AppData-main/StructureDefinition-at-prenudge-sitting-hours-observation.xlsx
+++ b/r4-JoanneumResearch-PreNUDGE-AppData-main/StructureDefinition-at-prenudge-sitting-hours-observation.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2609" uniqueCount="553">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2609" uniqueCount="554">
   <si>
     <t>Property</t>
   </si>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-26T07:28:06+00:00</t>
+    <t>2026-10-21T09:39:19+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -1515,6 +1515,10 @@
   <si>
     <t xml:space="preserve">obs-3
 </t>
+  </si>
+  <si>
+    <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
+sqty-1:The comparator is not used on a SimpleQuantity {comparator.empty()}</t>
   </si>
   <si>
     <t>OBX-7</t>
@@ -8251,7 +8255,7 @@
         <v>479</v>
       </c>
       <c r="AJ51" t="s" s="2">
-        <v>105</v>
+        <v>480</v>
       </c>
       <c r="AK51" t="s" s="2">
         <v>21</v>
@@ -8260,10 +8264,10 @@
         <v>21</v>
       </c>
       <c r="AM51" t="s" s="2">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="AN51" t="s" s="2">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="AO51" t="s" s="2">
         <v>21</v>
@@ -8274,10 +8278,10 @@
     </row>
     <row r="52" hidden="true">
       <c r="A52" t="s" s="2">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
@@ -8303,10 +8307,10 @@
         <v>476</v>
       </c>
       <c r="L52" t="s" s="2">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="M52" t="s" s="2">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="N52" s="2"/>
       <c r="O52" s="2"/>
@@ -8357,7 +8361,7 @@
         <v>21</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>81</v>
@@ -8369,7 +8373,7 @@
         <v>479</v>
       </c>
       <c r="AJ52" t="s" s="2">
-        <v>105</v>
+        <v>480</v>
       </c>
       <c r="AK52" t="s" s="2">
         <v>21</v>
@@ -8378,10 +8382,10 @@
         <v>21</v>
       </c>
       <c r="AM52" t="s" s="2">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="AN52" t="s" s="2">
-        <v>485</v>
+        <v>486</v>
       </c>
       <c r="AO52" t="s" s="2">
         <v>21</v>
@@ -8392,10 +8396,10 @@
     </row>
     <row r="53" hidden="true">
       <c r="A53" t="s" s="2">
-        <v>486</v>
+        <v>487</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>486</v>
+        <v>487</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
@@ -8421,16 +8425,16 @@
         <v>182</v>
       </c>
       <c r="L53" t="s" s="2">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="M53" t="s" s="2">
-        <v>488</v>
+        <v>489</v>
       </c>
       <c r="N53" t="s" s="2">
-        <v>489</v>
+        <v>490</v>
       </c>
       <c r="O53" t="s" s="2">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="P53" t="s" s="2">
         <v>21</v>
@@ -8458,10 +8462,10 @@
         <v>117</v>
       </c>
       <c r="Y53" t="s" s="2">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="Z53" t="s" s="2">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="AA53" t="s" s="2">
         <v>21</v>
@@ -8479,7 +8483,7 @@
         <v>21</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>486</v>
+        <v>487</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>81</v>
@@ -8497,10 +8501,10 @@
         <v>21</v>
       </c>
       <c r="AL53" t="s" s="2">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="AM53" t="s" s="2">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="AN53" t="s" s="2">
         <v>413</v>
@@ -8514,10 +8518,10 @@
     </row>
     <row r="54" hidden="true">
       <c r="A54" t="s" s="2">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
@@ -8543,16 +8547,16 @@
         <v>182</v>
       </c>
       <c r="L54" t="s" s="2">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="M54" t="s" s="2">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="N54" t="s" s="2">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="O54" t="s" s="2">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="P54" t="s" s="2">
         <v>21</v>
@@ -8580,10 +8584,10 @@
         <v>270</v>
       </c>
       <c r="Y54" t="s" s="2">
-        <v>500</v>
+        <v>501</v>
       </c>
       <c r="Z54" t="s" s="2">
-        <v>501</v>
+        <v>502</v>
       </c>
       <c r="AA54" t="s" s="2">
         <v>21</v>
@@ -8601,7 +8605,7 @@
         <v>21</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>81</v>
@@ -8619,10 +8623,10 @@
         <v>21</v>
       </c>
       <c r="AL54" t="s" s="2">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="AM54" t="s" s="2">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="AN54" t="s" s="2">
         <v>413</v>
@@ -8636,10 +8640,10 @@
     </row>
     <row r="55" hidden="true">
       <c r="A55" t="s" s="2">
-        <v>502</v>
+        <v>503</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>502</v>
+        <v>503</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
@@ -8662,17 +8666,17 @@
         <v>21</v>
       </c>
       <c r="K55" t="s" s="2">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="L55" t="s" s="2">
-        <v>504</v>
+        <v>505</v>
       </c>
       <c r="M55" t="s" s="2">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="N55" s="2"/>
       <c r="O55" t="s" s="2">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="P55" t="s" s="2">
         <v>21</v>
@@ -8721,7 +8725,7 @@
         <v>21</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>502</v>
+        <v>503</v>
       </c>
       <c r="AG55" t="s" s="2">
         <v>81</v>
@@ -8745,7 +8749,7 @@
         <v>21</v>
       </c>
       <c r="AN55" t="s" s="2">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="AO55" t="s" s="2">
         <v>21</v>
@@ -8756,10 +8760,10 @@
     </row>
     <row r="56" hidden="true">
       <c r="A56" t="s" s="2">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
@@ -8785,10 +8789,10 @@
         <v>160</v>
       </c>
       <c r="L56" t="s" s="2">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="M56" t="s" s="2">
-        <v>510</v>
+        <v>511</v>
       </c>
       <c r="N56" s="2"/>
       <c r="O56" s="2"/>
@@ -8839,7 +8843,7 @@
         <v>21</v>
       </c>
       <c r="AF56" t="s" s="2">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="AG56" t="s" s="2">
         <v>81</v>
@@ -8860,10 +8864,10 @@
         <v>21</v>
       </c>
       <c r="AM56" t="s" s="2">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="AN56" t="s" s="2">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="AO56" t="s" s="2">
         <v>21</v>
@@ -8874,10 +8878,10 @@
     </row>
     <row r="57" hidden="true">
       <c r="A57" t="s" s="2">
-        <v>512</v>
+        <v>513</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>512</v>
+        <v>513</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
@@ -8900,16 +8904,16 @@
         <v>94</v>
       </c>
       <c r="K57" t="s" s="2">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="L57" t="s" s="2">
-        <v>514</v>
+        <v>515</v>
       </c>
       <c r="M57" t="s" s="2">
-        <v>515</v>
+        <v>516</v>
       </c>
       <c r="N57" t="s" s="2">
-        <v>516</v>
+        <v>517</v>
       </c>
       <c r="O57" s="2"/>
       <c r="P57" t="s" s="2">
@@ -8959,7 +8963,7 @@
         <v>21</v>
       </c>
       <c r="AF57" t="s" s="2">
-        <v>512</v>
+        <v>513</v>
       </c>
       <c r="AG57" t="s" s="2">
         <v>81</v>
@@ -8980,10 +8984,10 @@
         <v>21</v>
       </c>
       <c r="AM57" t="s" s="2">
-        <v>517</v>
+        <v>518</v>
       </c>
       <c r="AN57" t="s" s="2">
-        <v>518</v>
+        <v>519</v>
       </c>
       <c r="AO57" t="s" s="2">
         <v>21</v>
@@ -8994,10 +8998,10 @@
     </row>
     <row r="58">
       <c r="A58" t="s" s="2">
-        <v>519</v>
+        <v>520</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>519</v>
+        <v>520</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
@@ -9020,16 +9024,16 @@
         <v>94</v>
       </c>
       <c r="K58" t="s" s="2">
-        <v>520</v>
+        <v>521</v>
       </c>
       <c r="L58" t="s" s="2">
-        <v>521</v>
+        <v>522</v>
       </c>
       <c r="M58" t="s" s="2">
-        <v>522</v>
+        <v>523</v>
       </c>
       <c r="N58" t="s" s="2">
-        <v>523</v>
+        <v>524</v>
       </c>
       <c r="O58" s="2"/>
       <c r="P58" t="s" s="2">
@@ -9079,7 +9083,7 @@
         <v>21</v>
       </c>
       <c r="AF58" t="s" s="2">
-        <v>519</v>
+        <v>520</v>
       </c>
       <c r="AG58" t="s" s="2">
         <v>81</v>
@@ -9100,10 +9104,10 @@
         <v>21</v>
       </c>
       <c r="AM58" t="s" s="2">
-        <v>517</v>
+        <v>518</v>
       </c>
       <c r="AN58" t="s" s="2">
-        <v>524</v>
+        <v>525</v>
       </c>
       <c r="AO58" t="s" s="2">
         <v>21</v>
@@ -9114,10 +9118,10 @@
     </row>
     <row r="59" hidden="true">
       <c r="A59" t="s" s="2">
-        <v>525</v>
+        <v>526</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>525</v>
+        <v>526</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
@@ -9143,16 +9147,16 @@
         <v>460</v>
       </c>
       <c r="L59" t="s" s="2">
-        <v>526</v>
+        <v>527</v>
       </c>
       <c r="M59" t="s" s="2">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="N59" t="s" s="2">
-        <v>528</v>
+        <v>529</v>
       </c>
       <c r="O59" t="s" s="2">
-        <v>529</v>
+        <v>530</v>
       </c>
       <c r="P59" t="s" s="2">
         <v>21</v>
@@ -9201,7 +9205,7 @@
         <v>21</v>
       </c>
       <c r="AF59" t="s" s="2">
-        <v>525</v>
+        <v>526</v>
       </c>
       <c r="AG59" t="s" s="2">
         <v>81</v>
@@ -9222,10 +9226,10 @@
         <v>21</v>
       </c>
       <c r="AM59" t="s" s="2">
-        <v>530</v>
+        <v>531</v>
       </c>
       <c r="AN59" t="s" s="2">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="AO59" t="s" s="2">
         <v>21</v>
@@ -9236,10 +9240,10 @@
     </row>
     <row r="60" hidden="true">
       <c r="A60" t="s" s="2">
-        <v>532</v>
+        <v>533</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>532</v>
+        <v>533</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
@@ -9354,10 +9358,10 @@
     </row>
     <row r="61" hidden="true">
       <c r="A61" t="s" s="2">
-        <v>533</v>
+        <v>534</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>533</v>
+        <v>534</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
@@ -9474,10 +9478,10 @@
     </row>
     <row r="62" hidden="true">
       <c r="A62" t="s" s="2">
-        <v>534</v>
+        <v>535</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>534</v>
+        <v>535</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
@@ -9596,10 +9600,10 @@
     </row>
     <row r="63" hidden="true">
       <c r="A63" t="s" s="2">
-        <v>535</v>
+        <v>536</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>535</v>
+        <v>536</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
@@ -9625,13 +9629,13 @@
         <v>182</v>
       </c>
       <c r="L63" t="s" s="2">
-        <v>536</v>
+        <v>537</v>
       </c>
       <c r="M63" t="s" s="2">
-        <v>537</v>
+        <v>538</v>
       </c>
       <c r="N63" t="s" s="2">
-        <v>538</v>
+        <v>539</v>
       </c>
       <c r="O63" t="s" s="2">
         <v>268</v>
@@ -9683,7 +9687,7 @@
         <v>21</v>
       </c>
       <c r="AF63" t="s" s="2">
-        <v>535</v>
+        <v>536</v>
       </c>
       <c r="AG63" t="s" s="2">
         <v>93</v>
@@ -9701,7 +9705,7 @@
         <v>21</v>
       </c>
       <c r="AL63" t="s" s="2">
-        <v>539</v>
+        <v>540</v>
       </c>
       <c r="AM63" t="s" s="2">
         <v>275</v>
@@ -9718,10 +9722,10 @@
     </row>
     <row r="64" hidden="true">
       <c r="A64" t="s" s="2">
-        <v>540</v>
+        <v>541</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>540</v>
+        <v>541</v>
       </c>
       <c r="C64" s="2"/>
       <c r="D64" t="s" s="2">
@@ -9744,16 +9748,16 @@
         <v>94</v>
       </c>
       <c r="K64" t="s" s="2">
-        <v>541</v>
+        <v>542</v>
       </c>
       <c r="L64" t="s" s="2">
-        <v>542</v>
+        <v>543</v>
       </c>
       <c r="M64" t="s" s="2">
         <v>342</v>
       </c>
       <c r="N64" t="s" s="2">
-        <v>543</v>
+        <v>544</v>
       </c>
       <c r="O64" t="s" s="2">
         <v>344</v>
@@ -9805,7 +9809,7 @@
         <v>21</v>
       </c>
       <c r="AF64" t="s" s="2">
-        <v>540</v>
+        <v>541</v>
       </c>
       <c r="AG64" t="s" s="2">
         <v>81</v>
@@ -9823,7 +9827,7 @@
         <v>21</v>
       </c>
       <c r="AL64" t="s" s="2">
-        <v>544</v>
+        <v>545</v>
       </c>
       <c r="AM64" t="s" s="2">
         <v>347</v>
@@ -9840,10 +9844,10 @@
     </row>
     <row r="65">
       <c r="A65" t="s" s="2">
-        <v>545</v>
+        <v>546</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>545</v>
+        <v>546</v>
       </c>
       <c r="C65" s="2"/>
       <c r="D65" t="s" s="2">
@@ -9869,13 +9873,13 @@
         <v>182</v>
       </c>
       <c r="L65" t="s" s="2">
-        <v>546</v>
+        <v>547</v>
       </c>
       <c r="M65" t="s" s="2">
-        <v>547</v>
+        <v>548</v>
       </c>
       <c r="N65" t="s" s="2">
-        <v>548</v>
+        <v>549</v>
       </c>
       <c r="O65" t="s" s="2">
         <v>398</v>
@@ -9927,7 +9931,7 @@
         <v>21</v>
       </c>
       <c r="AF65" t="s" s="2">
-        <v>545</v>
+        <v>546</v>
       </c>
       <c r="AG65" t="s" s="2">
         <v>81</v>
@@ -9962,10 +9966,10 @@
     </row>
     <row r="66" hidden="true">
       <c r="A66" t="s" s="2">
-        <v>549</v>
+        <v>550</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>549</v>
+        <v>550</v>
       </c>
       <c r="C66" s="2"/>
       <c r="D66" t="s" s="2">
@@ -10049,7 +10053,7 @@
         <v>21</v>
       </c>
       <c r="AF66" t="s" s="2">
-        <v>549</v>
+        <v>550</v>
       </c>
       <c r="AG66" t="s" s="2">
         <v>81</v>
@@ -10084,10 +10088,10 @@
     </row>
     <row r="67" hidden="true">
       <c r="A67" t="s" s="2">
-        <v>550</v>
+        <v>551</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>550</v>
+        <v>551</v>
       </c>
       <c r="C67" s="2"/>
       <c r="D67" t="s" s="2">
@@ -10113,10 +10117,10 @@
         <v>83</v>
       </c>
       <c r="L67" t="s" s="2">
-        <v>551</v>
+        <v>552</v>
       </c>
       <c r="M67" t="s" s="2">
-        <v>552</v>
+        <v>553</v>
       </c>
       <c r="N67" t="s" s="2">
         <v>463</v>
@@ -10171,7 +10175,7 @@
         <v>21</v>
       </c>
       <c r="AF67" t="s" s="2">
-        <v>550</v>
+        <v>551</v>
       </c>
       <c r="AG67" t="s" s="2">
         <v>81</v>
